--- a/archive/Survivor_2026-10-04_2031_PT.xlsx
+++ b/archive/Survivor_2026-10-04_2031_PT.xlsx
@@ -776,7 +776,7 @@
         <v>0.1541614263711546</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1794806929508048</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0.02698218328050483</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.3463971227760583</v>
+        <v>0.3463971259088848</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.3464512165360852</v>
+        <v>0.3464512062651334</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.3463971227760583</v>
+        <v>0.3463971259088848</v>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.1982245316673374</v>
+        <v>0.1982246540542743</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.3542858650441819</v>
+        <v>0.3542858700688071</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.3583095243242682</v>
+        <v>0.3583095554429965</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3542858650441819</v>
+        <v>0.3542858700688071</v>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.09395900696350357</v>
+        <v>-0.09395908779788664</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.0920150317138323</v>
+        <v>-0.09201495053219366</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.04348363049110981</v>
+        <v>-0.0434835449703479</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.086351520867891</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.08244932626463886</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>-0.05073765883132797</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="AL4" s="4" t="n">
-        <v>-0.04348363049110981</v>
+        <v>-0.0434835449703479</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="4" t="n">
-        <v>-0.01880306629622497</v>
+        <v>-0.01880289296518045</v>
       </c>
       <c r="AQ4" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06715312741714952</v>
+        <v>0.0671532403865378</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.007531580325343068</v>
@@ -1450,10 +1450,10 @@
         <v>0.0317613578135878</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02275371772858681</v>
+        <v>-0.02275381246463382</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>-0.02348389703176146</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03715196348622696</v>
+        <v>0.03715185591311232</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>-0.007071979722355071</v>
+        <v>-0.007072079904586248</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -1612,10 +1612,10 @@
         <v>0.3977141325510336</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.4464097340653188</v>
+        <v>0.4464096070240571</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.07424705021970102</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4639560631420809</v>
+        <v>0.4639559345596878</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2993170121797599</v>
+        <v>0.2993170040223082</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.2952392591396466</v>
+        <v>0.2952392382918702</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2993170121797599</v>
+        <v>0.2993170040223082</v>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AK7" s="2" t="n"/>
       <c r="AL7" s="3" t="n">
-        <v>0.4900491624844652</v>
+        <v>0.4900490316102593</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0.07693018597033974</v>
+        <v>0.07693017783949019</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0.02285226703064946</v>
@@ -1787,7 +1787,7 @@
         <v>0.002883993594746892</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02833397862188713</v>
+        <v>-0.02833390943374015</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-0.033330928240068</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>-0.00744549208068257</v>
+        <v>-0.007445564518826053</v>
       </c>
       <c r="AQ8" s="4" t="n">
         <v>0.02285226703064946</v>
@@ -2115,13 +2115,13 @@
         <v>0.06008271542783095</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.03786890845253477</v>
+        <v>0.03786882663086688</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03455995928147937</v>
+        <v>0.03455987772067659</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824857836371097</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.009142235324292258</v>
@@ -2484,7 +2484,7 @@
         <v>0.02698218328050483</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.1794808032758544</v>
+        <v>0.1794806929508048</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         <v>-0.05073765883132797</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-0.08244924336347392</v>
+        <v>-0.08244932626463886</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.08635160306540612</v>
+        <v>-0.086351520867891</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         <v>-0.02348389703176146</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-0.02275371772858681</v>
+        <v>-0.02275381246463382</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.004162036248914869</v>
+        <v>-0.004162134623879599</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>-0.033330928240068</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.02833397862188713</v>
+        <v>-0.02833390943374015</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>0.009142235324292258</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.01824849960638542</v>
+        <v>0.01824857836371097</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
